--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/3406-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/3406-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1377B8E2-3CAE-438F-82F9-681566C2D1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8AA3FD4F-4E31-4AE6-99B0-77D8E898DF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{4449B296-DD8D-415C-BCE5-8BBF2DE840F9}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{7D7F5816-C6CC-4615-8896-DF0BC23D7F8E}"/>
   </bookViews>
   <sheets>
     <sheet name="3406-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1484,25 +1484,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C658FA6E-164E-443B-B09C-A16D9F252A8A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEC75540-C255-4E57-8B5E-4E50733BB829}">
   <dimension ref="A1:R47"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1530,7 +1530,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1560,7 +1560,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1656,7 +1656,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1710,7 +1710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="39">
         <v>2025</v>
       </c>
@@ -1820,7 +1820,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2024</v>
       </c>
@@ -2042,7 +2042,7 @@
         <v>1.98</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2098,7 +2098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2154,7 +2154,7 @@
         <v>1.98</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2210,7 +2210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="39">
         <v>2023</v>
       </c>
@@ -2264,7 +2264,7 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>26</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>26</v>
       </c>
@@ -2376,7 +2376,7 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>26</v>
       </c>
@@ -2432,7 +2432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="37">
         <v>2022</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>26</v>
       </c>
@@ -2542,7 +2542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>26</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>26</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="39">
         <v>2021</v>
       </c>
@@ -2708,7 +2708,7 @@
         <v>1.89</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>26</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>26</v>
       </c>
@@ -2820,7 +2820,7 @@
         <v>1.89</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
         <v>26</v>
       </c>
@@ -2876,7 +2876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="37">
         <v>2020</v>
       </c>
@@ -2930,7 +2930,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>26</v>
       </c>
@@ -2986,7 +2986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>26</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2019</v>
       </c>
@@ -3096,7 +3096,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>26</v>
       </c>
@@ -3152,7 +3152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>26</v>
       </c>
@@ -3208,7 +3208,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="37">
         <v>2018</v>
       </c>
@@ -3262,7 +3262,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="39">
         <v>2017</v>
       </c>
@@ -3316,7 +3316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>2016</v>
       </c>
@@ -3370,7 +3370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="39">
         <v>2015</v>
       </c>
@@ -3424,7 +3424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
         <v>2014</v>
       </c>
@@ -3478,7 +3478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="39">
         <v>2013</v>
       </c>
@@ -3532,7 +3532,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="37">
         <v>2012</v>
       </c>
@@ -3586,7 +3586,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="39">
         <v>2011</v>
       </c>
@@ -3640,7 +3640,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="37">
         <v>2010</v>
       </c>
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="39">
         <v>2009</v>
       </c>
@@ -3748,7 +3748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="37">
         <v>2008</v>
       </c>
@@ -3802,7 +3802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="39">
         <v>2007</v>
       </c>
@@ -3856,7 +3856,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="37">
         <v>2006</v>
       </c>
@@ -3910,7 +3910,7 @@
         <v>5.33</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="39">
         <v>2005</v>
       </c>
@@ -3964,7 +3964,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="37" t="s">
         <v>47</v>
       </c>
